--- a/Gestion Stock 2025/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2025.xlsx
+++ b/Gestion Stock 2025/Gestion de Stock Zoubiria/Suivie pose Compteur Zoubiria 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2025\Gestion de Stock Zoubiria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2CFAAD-5D09-4804-B625-0ACA634FA9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970DCC4C-CC56-4D40-81C7-81EBB78B6BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2024" sheetId="12" r:id="rId1"/>
@@ -15068,7 +15068,9 @@
       <c r="H9" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <v>2025118581</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
     </row>
